--- a/Project 2 - Unstructured Wave Equation/SimResults.xlsx
+++ b/Project 2 - Unstructured Wave Equation/SimResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveconcordia-my.sharepoint.com/personal/c_rowsel_live_concordia_ca/Documents/Documents/School/Winter 2023/Mech-588/Project 2 - Unstructured Wave Equation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{38B4D2F9-0DCE-4293-BB40-FC52B6B555A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E96340C4-79B7-4106-85F4-C1CE8E9BF1D2}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{38B4D2F9-0DCE-4293-BB40-FC52B6B555A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42E08280-A208-4239-9C51-5DB727740378}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="3615" windowWidth="13950" windowHeight="11040" xr2:uid="{E75B3FFA-0839-405F-9DF7-E4C6318DF95A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E75B3FFA-0839-405F-9DF7-E4C6318DF95A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -767,7 +767,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.39833148579531846</c:v>
+                  <c:v>6.3639610306789276</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.79163909484037642</c:v>
@@ -832,7 +832,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.39833148579531846</c:v>
+                  <c:v>6.3639610306789276</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.79163909484037642</c:v>
@@ -890,50 +890,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$R$10:$S$10</c:f>
@@ -941,7 +897,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.39833148579531846</c:v>
+                  <c:v>6.3639610306789276</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.79163909484037642</c:v>
@@ -1757,6 +1713,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2267,7 +2227,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="8">
-        <v>8.0389675954067625E-4</v>
+        <v>8.0389675954067603E-4</v>
       </c>
       <c r="O4" s="23">
         <v>0.368751034837</v>
@@ -2332,7 +2292,7 @@
       </c>
       <c r="N5" s="8">
         <f>N4</f>
-        <v>8.0389675954067625E-4</v>
+        <v>8.0389675954067603E-4</v>
       </c>
       <c r="O5" s="23">
         <v>0.3688323959357</v>
@@ -2381,7 +2341,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="9">
-        <v>8.0389675954067625E-4</v>
+        <v>8.0389675954067603E-4</v>
       </c>
       <c r="O6" s="24">
         <v>0.3688323959357</v>
@@ -2528,11 +2488,10 @@
       <c r="N10" s="9"/>
       <c r="O10" s="12"/>
       <c r="R10" s="36">
-        <f t="shared" ref="R10" si="2">36/SQRT(R$2)</f>
-        <v>0.39833148579531846</v>
+        <v>6.3639610306789276</v>
       </c>
       <c r="S10" s="31">
-        <f t="shared" ref="S10" si="3">36/SQRT(S$2)</f>
+        <f t="shared" ref="S10" si="2">36/SQRT(S$2)</f>
         <v>0.79163909484037642</v>
       </c>
     </row>
@@ -2652,7 +2611,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" ref="H13:H14" si="4">$T$4</f>
+        <f t="shared" ref="H13:H14" si="3">$T$4</f>
         <v>2.0460290364053405E-4</v>
       </c>
       <c r="I13" s="23">
@@ -2662,7 +2621,7 @@
         <v>4</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" ref="K13:K14" si="5">$U$4</f>
+        <f t="shared" ref="K13:K14" si="4">$U$4</f>
         <v>3.8994720607976119E-4</v>
       </c>
       <c r="L13" s="11"/>
@@ -2670,7 +2629,7 @@
         <v>4</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" ref="N13:N14" si="6">$V$4</f>
+        <f t="shared" ref="N13:N14" si="5">$V$4</f>
         <v>8.0389675954067625E-4</v>
       </c>
       <c r="O13" s="11"/>
@@ -2704,7 +2663,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.0460290364053405E-4</v>
       </c>
       <c r="I14" s="24">
@@ -2714,7 +2673,7 @@
         <v>5</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.8994720607976119E-4</v>
       </c>
       <c r="L14" s="24">
@@ -2724,7 +2683,7 @@
         <v>5</v>
       </c>
       <c r="N14" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.0389675954067625E-4</v>
       </c>
       <c r="O14" s="12"/>
